--- a/Res_ConvLSTM/DroughtDataset_model_testing_1754912235_individual_h_3.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1754912235_individual_h_3.xlsx
@@ -658,7 +658,7 @@
         <v>0.008429030597149695</v>
       </c>
       <c r="C2" t="n">
-        <v>18938934</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>18938934</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>14389958</v>
+        <v>4638157</v>
       </c>
       <c r="L2" t="n">
-        <v>8820149</v>
+        <v>2705260</v>
       </c>
       <c r="M2" t="n">
-        <v>2164237</v>
+        <v>641962</v>
       </c>
       <c r="N2" t="n">
-        <v>110952</v>
+        <v>28315</v>
       </c>
       <c r="O2" t="n">
-        <v>1267849</v>
+        <v>377181</v>
       </c>
       <c r="P2" t="n">
-        <v>487784</v>
+        <v>150891</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9998921155929565</v>
+        <v>0.9998916387557983</v>
       </c>
       <c r="R2" t="n">
-        <v>0.947020947933197</v>
+        <v>0.9078369140625</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8799651265144348</v>
+        <v>0.8158766031265259</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8644879460334778</v>
+        <v>0.7708172202110291</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3170229196548462</v>
+        <v>0.2392156571149826</v>
       </c>
       <c r="V2" t="n">
-        <v>0.8743279576301575</v>
+        <v>0.8044554591178894</v>
       </c>
       <c r="W2" t="n">
-        <v>0.9273459911346436</v>
+        <v>0.8819754123687744</v>
       </c>
       <c r="X2" t="n">
-        <v>18938934</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>18938934</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>14462079</v>
+        <v>4815402</v>
       </c>
       <c r="AG2" t="n">
-        <v>8899088</v>
+        <v>2970254</v>
       </c>
       <c r="AH2" t="n">
-        <v>2397713</v>
+        <v>799435</v>
       </c>
       <c r="AI2" t="n">
-        <v>176916</v>
+        <v>58995</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1376789</v>
+        <v>459097</v>
       </c>
       <c r="AK2" t="n">
-        <v>540046</v>
+        <v>180028</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9566799402236938</v>
+        <v>0.9565494656562805</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9112439155578613</v>
+        <v>0.9113017320632935</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8581776022911072</v>
+        <v>0.8579359650611877</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6626315712928772</v>
+        <v>0.6623888611793518</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020464420318604</v>
+        <v>0.9020065665245056</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314221143722534</v>
+        <v>0.9314266443252563</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002021254280242989</v>
       </c>
       <c r="C3" t="n">
-        <v>596</v>
+        <v>202</v>
       </c>
       <c r="D3" t="n">
-        <v>14389958</v>
+        <v>4638157</v>
       </c>
       <c r="E3" t="n">
-        <v>703944</v>
+        <v>386518</v>
       </c>
       <c r="F3" t="n">
-        <v>5746</v>
+        <v>3096</v>
       </c>
       <c r="G3" t="n">
-        <v>1136</v>
+        <v>543</v>
       </c>
       <c r="H3" t="n">
-        <v>316</v>
+        <v>173</v>
       </c>
       <c r="I3" t="n">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="J3" t="n">
-        <v>30047822</v>
+        <v>10015938</v>
       </c>
       <c r="K3" t="n">
-        <v>33082047</v>
+        <v>10830035</v>
       </c>
       <c r="L3" t="n">
-        <v>38006793</v>
+        <v>12454897</v>
       </c>
       <c r="M3" t="n">
-        <v>45854261</v>
+        <v>15206609</v>
       </c>
       <c r="N3" t="n">
-        <v>48482573</v>
+        <v>16150420</v>
       </c>
       <c r="O3" t="n">
-        <v>47279629</v>
+        <v>15728738</v>
       </c>
       <c r="P3" t="n">
-        <v>48370738</v>
+        <v>16116107</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9528676867485046</v>
+        <v>0.9223368167877197</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9019606709480286</v>
+        <v>0.8287686705589294</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7742452621459961</v>
+        <v>0.6887117624282837</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4152426421642303</v>
+        <v>0.317685604095459</v>
       </c>
       <c r="V3" t="n">
-        <v>0.830322265625</v>
+        <v>0.7407644987106323</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8412302732467651</v>
+        <v>0.7806012630462646</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>14462079</v>
+        <v>4815402</v>
       </c>
       <c r="Z3" t="n">
-        <v>593526</v>
+        <v>197896</v>
       </c>
       <c r="AA3" t="n">
-        <v>25572</v>
+        <v>8540</v>
       </c>
       <c r="AB3" t="n">
-        <v>20336</v>
+        <v>6789</v>
       </c>
       <c r="AC3" t="n">
-        <v>135</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>30049866</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>33232195</v>
+        <v>11082162</v>
       </c>
       <c r="AG3" t="n">
-        <v>38343158</v>
+        <v>12776309</v>
       </c>
       <c r="AH3" t="n">
-        <v>45797268</v>
+        <v>15265103</v>
       </c>
       <c r="AI3" t="n">
-        <v>48631528</v>
+        <v>16210402</v>
       </c>
       <c r="AJ3" t="n">
-        <v>47312358</v>
+        <v>15770546</v>
       </c>
       <c r="AK3" t="n">
-        <v>48369192</v>
+        <v>16123045</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9576433300971985</v>
+        <v>0.957583487033844</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.910033106803894</v>
+        <v>0.9099507331848145</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8577702045440674</v>
+        <v>0.8576524257659912</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.662115752696991</v>
+        <v>0.6619057655334473</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9016677737236023</v>
+        <v>0.9016434550285339</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9313610792160034</v>
+        <v>0.9313350915908813</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03189760997342238</v>
       </c>
       <c r="C4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D4" t="n">
-        <v>748258</v>
+        <v>441588</v>
       </c>
       <c r="E4" t="n">
-        <v>8820149</v>
+        <v>2705260</v>
       </c>
       <c r="F4" t="n">
-        <v>199452</v>
+        <v>109235</v>
       </c>
       <c r="G4" t="n">
-        <v>6016</v>
+        <v>4092</v>
       </c>
       <c r="H4" t="n">
-        <v>4690</v>
+        <v>3769</v>
       </c>
       <c r="I4" t="n">
-        <v>281</v>
+        <v>236</v>
       </c>
       <c r="J4" t="n">
-        <v>2044</v>
+        <v>684</v>
       </c>
       <c r="K4" t="n">
-        <v>805015</v>
+        <v>470863</v>
       </c>
       <c r="L4" t="n">
-        <v>1203145</v>
+        <v>610511</v>
       </c>
       <c r="M4" t="n">
-        <v>339253</v>
+        <v>190871</v>
       </c>
       <c r="N4" t="n">
-        <v>239029</v>
+        <v>90051</v>
       </c>
       <c r="O4" t="n">
-        <v>182235</v>
+        <v>91684</v>
       </c>
       <c r="P4" t="n">
-        <v>38216</v>
+        <v>20192</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999460577964783</v>
+        <v>0.9999458193778992</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9499353170394897</v>
+        <v>0.9150294065475464</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8908271789550781</v>
+        <v>0.8222721219062805</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8168818950653076</v>
+        <v>0.7274551391601562</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3595455884933472</v>
+        <v>0.2729222476482391</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8517571091651917</v>
+        <v>0.7712973952293396</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8821915984153748</v>
+        <v>0.8281977772712708</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>611398</v>
+        <v>204218</v>
       </c>
       <c r="Z4" t="n">
-        <v>8899088</v>
+        <v>2970254</v>
       </c>
       <c r="AA4" t="n">
-        <v>248302</v>
+        <v>83015</v>
       </c>
       <c r="AB4" t="n">
-        <v>16438</v>
+        <v>5489</v>
       </c>
       <c r="AC4" t="n">
-        <v>3432</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>204</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>654867</v>
+        <v>218736</v>
       </c>
       <c r="AG4" t="n">
-        <v>866780</v>
+        <v>289099</v>
       </c>
       <c r="AH4" t="n">
-        <v>396246</v>
+        <v>132377</v>
       </c>
       <c r="AI4" t="n">
-        <v>90074</v>
+        <v>30069</v>
       </c>
       <c r="AJ4" t="n">
-        <v>149506</v>
+        <v>49876</v>
       </c>
       <c r="AK4" t="n">
-        <v>39762</v>
+        <v>13254</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9571613669395447</v>
+        <v>0.9570662379264832</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106380939483643</v>
+        <v>0.910625696182251</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8579738140106201</v>
+        <v>0.8577942252159119</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6623735427856445</v>
+        <v>0.6621472835540771</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9018570184707642</v>
+        <v>0.9018250107765198</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313915967941284</v>
+        <v>0.9313808679580688</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>541</v>
+        <v>191</v>
       </c>
       <c r="D5" t="n">
-        <v>34874</v>
+        <v>17519</v>
       </c>
       <c r="E5" t="n">
-        <v>430858</v>
+        <v>200206</v>
       </c>
       <c r="F5" t="n">
-        <v>2164237</v>
+        <v>641962</v>
       </c>
       <c r="G5" t="n">
-        <v>97999</v>
+        <v>31200</v>
       </c>
       <c r="H5" t="n">
-        <v>64409</v>
+        <v>39247</v>
       </c>
       <c r="I5" t="n">
-        <v>2368</v>
+        <v>1795</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>711780</v>
+        <v>390545</v>
       </c>
       <c r="L5" t="n">
-        <v>958713</v>
+        <v>558932</v>
       </c>
       <c r="M5" t="n">
-        <v>631049</v>
+        <v>290158</v>
       </c>
       <c r="N5" t="n">
-        <v>156246</v>
+        <v>60814</v>
       </c>
       <c r="O5" t="n">
-        <v>259087</v>
+        <v>131997</v>
       </c>
       <c r="P5" t="n">
-        <v>92062</v>
+        <v>42410</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999582767486572</v>
+        <v>0.9999580979347229</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9690379500389099</v>
+        <v>0.9472486972808838</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9558703899383545</v>
+        <v>0.9283850789070129</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9801933765411377</v>
+        <v>0.9705424904823303</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9919313192367554</v>
+        <v>0.9907612800598145</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9909913539886475</v>
+        <v>0.9863021373748779</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9973406791687012</v>
+        <v>0.9961663484573364</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>23984</v>
+        <v>8010</v>
       </c>
       <c r="Z5" t="n">
-        <v>254565</v>
+        <v>84966</v>
       </c>
       <c r="AA5" t="n">
-        <v>2397713</v>
+        <v>799435</v>
       </c>
       <c r="AB5" t="n">
-        <v>29795</v>
+        <v>9941</v>
       </c>
       <c r="AC5" t="n">
-        <v>87330</v>
+        <v>29135</v>
       </c>
       <c r="AD5" t="n">
-        <v>1899</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>639659</v>
+        <v>213300</v>
       </c>
       <c r="AG5" t="n">
-        <v>879774</v>
+        <v>293938</v>
       </c>
       <c r="AH5" t="n">
-        <v>397573</v>
+        <v>132685</v>
       </c>
       <c r="AI5" t="n">
-        <v>90282</v>
+        <v>30134</v>
       </c>
       <c r="AJ5" t="n">
-        <v>150147</v>
+        <v>50081</v>
       </c>
       <c r="AK5" t="n">
-        <v>39800</v>
+        <v>13273</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735750555992126</v>
+        <v>0.9735427498817444</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9643478989601135</v>
+        <v>0.9642956852912903</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837958812713623</v>
+        <v>0.9837679862976074</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963183999061584</v>
+        <v>0.9963132739067078</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938832521438599</v>
+        <v>0.9938787817955017</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983758926391602</v>
+        <v>0.9983755350112915</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>109</v>
+        <v>42</v>
       </c>
       <c r="D6" t="n">
-        <v>21736</v>
+        <v>11681</v>
       </c>
       <c r="E6" t="n">
-        <v>61393</v>
+        <v>17904</v>
       </c>
       <c r="F6" t="n">
-        <v>46699</v>
+        <v>21646</v>
       </c>
       <c r="G6" t="n">
-        <v>110952</v>
+        <v>28315</v>
       </c>
       <c r="H6" t="n">
-        <v>25398</v>
+        <v>9030</v>
       </c>
       <c r="I6" t="n">
-        <v>911</v>
+        <v>511</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>19318</v>
+        <v>6452</v>
       </c>
       <c r="Z6" t="n">
-        <v>16016</v>
+        <v>5347</v>
       </c>
       <c r="AA6" t="n">
-        <v>32584</v>
+        <v>10875</v>
       </c>
       <c r="AB6" t="n">
-        <v>176916</v>
+        <v>58995</v>
       </c>
       <c r="AC6" t="n">
-        <v>20921</v>
+        <v>6979</v>
       </c>
       <c r="AD6" t="n">
-        <v>1443</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>129</v>
+        <v>42</v>
       </c>
       <c r="D7" t="n">
-        <v>81</v>
+        <v>46</v>
       </c>
       <c r="E7" t="n">
-        <v>6628</v>
+        <v>5652</v>
       </c>
       <c r="F7" t="n">
-        <v>85766</v>
+        <v>55658</v>
       </c>
       <c r="G7" t="n">
-        <v>131869</v>
+        <v>52962</v>
       </c>
       <c r="H7" t="n">
-        <v>1267849</v>
+        <v>377181</v>
       </c>
       <c r="I7" t="n">
-        <v>34614</v>
+        <v>17637</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>83</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>2430</v>
+        <v>809</v>
       </c>
       <c r="AA7" t="n">
-        <v>88798</v>
+        <v>29617</v>
       </c>
       <c r="AB7" t="n">
-        <v>22710</v>
+        <v>7585</v>
       </c>
       <c r="AC7" t="n">
-        <v>1376789</v>
+        <v>459097</v>
       </c>
       <c r="AD7" t="n">
-        <v>36126</v>
+        <v>12042</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>653</v>
+        <v>195</v>
       </c>
       <c r="D8" t="n">
-        <v>66</v>
+        <v>29</v>
       </c>
       <c r="E8" t="n">
-        <v>322</v>
+        <v>231</v>
       </c>
       <c r="F8" t="n">
-        <v>1590</v>
+        <v>1236</v>
       </c>
       <c r="G8" t="n">
-        <v>2009</v>
+        <v>1254</v>
       </c>
       <c r="H8" t="n">
-        <v>87422</v>
+        <v>39465</v>
       </c>
       <c r="I8" t="n">
-        <v>487784</v>
+        <v>150891</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>84</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>243</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>990</v>
+        <v>330</v>
       </c>
       <c r="AB8" t="n">
-        <v>795</v>
+        <v>265</v>
       </c>
       <c r="AC8" t="n">
-        <v>37688</v>
+        <v>12569</v>
       </c>
       <c r="AD8" t="n">
-        <v>540046</v>
+        <v>180028</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
